--- a/artfynd/Hötjärnberget artfynd.xlsx
+++ b/artfynd/Hötjärnberget artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY102"/>
+  <dimension ref="A1:AY100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>56824827</v>
+        <v>89046260</v>
       </c>
       <c r="B2" t="n">
-        <v>78739</v>
+        <v>92509</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>760</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hötjärnberget, Ång</t>
+          <t>Hötjärnsbergets nordsida, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>685176</v>
+        <v>684852</v>
       </c>
       <c r="R2" t="n">
-        <v>7095463</v>
+        <v>7095559</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
+          <t>2020-08-31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
+          <t>2020-08-31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,33 +759,40 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>barrnaturskog</t>
-        </is>
+          <t>lövrik, luckig gammal barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AN2" t="n">
+        <v>1</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>brandstubbe omgärdade av 3 gammeltallar</t>
+          <t>1 substratenheter # gammal sälg, 25 cm i diameter</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>56824857</v>
+        <v>89046257</v>
       </c>
       <c r="B3" t="n">
-        <v>80083</v>
+        <v>79406</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +800,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>864</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hötjärnberget, Ång</t>
+          <t>Hötjärnsbergets nordsida, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>684806</v>
+        <v>684808</v>
       </c>
       <c r="R3" t="n">
-        <v>7095721</v>
+        <v>7095549</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,12 +854,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
+          <t>2020-08-31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
+          <t>2020-08-31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -866,33 +873,40 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>barrnaturskog</t>
-        </is>
+          <t>lövrik, luckig gammal barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AN3" t="n">
+        <v>1</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>1 substratenheter # bark på urgammal vårtbjörk, 50 cm i diameter</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89046258</v>
+        <v>56824866</v>
       </c>
       <c r="B4" t="n">
-        <v>80049</v>
+        <v>91920</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,34 +914,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229748</v>
+        <v>1205</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hötjärnsbergets nordsida, Ång</t>
+          <t>Hötjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>684835</v>
+        <v>684881</v>
       </c>
       <c r="R4" t="n">
-        <v>7095545</v>
+        <v>7095539</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,12 +968,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -973,75 +987,71 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>lövrik, luckig gammal barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AN4" t="n">
-        <v>1</v>
+          <t>barrnaturskog</t>
+        </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>1 substratenheter # gammal sälg, 30 cm i diameter, lutande</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>56824828</v>
+        <v>87754500</v>
       </c>
       <c r="B5" t="n">
-        <v>80955</v>
+        <v>91920</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1049</v>
+        <v>1205</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hötjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>685204</v>
+        <v>684863</v>
       </c>
       <c r="R5" t="n">
-        <v>7095464</v>
+        <v>7095572</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,12 +1078,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
+          <t>2020-08-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
+          <t>2020-08-18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1082,38 +1092,33 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>högstubbe tall</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>56824870</v>
+        <v>89046256</v>
       </c>
       <c r="B6" t="n">
-        <v>80043</v>
+        <v>92886</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1121,34 +1126,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229497</v>
+        <v>4787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Granriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lactarius zonarioides</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Kühner &amp; Romagn.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hötjärnberget, Ång</t>
+          <t>Hötjärnsbergets nordsida, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>684918</v>
+        <v>684780</v>
       </c>
       <c r="R6" t="n">
-        <v>7095587</v>
+        <v>7095590</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1175,12 +1189,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
+          <t>2020-08-31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
+          <t>2020-08-31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1194,55 +1208,54 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>asp</t>
+          <t>gammal örtrik grannaturskog med gamla lövträd</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>56824869</v>
+        <v>56824865</v>
       </c>
       <c r="B7" t="n">
-        <v>80119</v>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1252,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>684918</v>
+        <v>684847</v>
       </c>
       <c r="R7" t="n">
-        <v>7095587</v>
+        <v>7095566</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1324,45 +1337,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>56824824</v>
+        <v>89046259</v>
       </c>
       <c r="B8" t="n">
-        <v>80083</v>
+        <v>80392</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hötjärnberget, Ång</t>
+          <t>Hötjärnsbergets nordsida, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>685178</v>
+        <v>684835</v>
       </c>
       <c r="R8" t="n">
-        <v>7095579</v>
+        <v>7095545</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,12 +1402,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
+          <t>2020-08-31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
+          <t>2020-08-31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1408,68 +1421,75 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>barrnaturskog</t>
-        </is>
+          <t>lövrik, luckig gammal barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AN8" t="n">
+        <v>1</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>1 substratenheter # gammal sälg, 30 cm i diameter, lutande</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>56824798</v>
+        <v>89046258</v>
       </c>
       <c r="B9" t="n">
-        <v>80083</v>
+        <v>80398</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>229748</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hötjärnberget, Ång</t>
+          <t>Hötjärnsbergets nordsida, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>685574</v>
+        <v>684835</v>
       </c>
       <c r="R9" t="n">
-        <v>7095206</v>
+        <v>7095545</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,12 +1516,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
+          <t>2020-08-31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
+          <t>2020-08-31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1515,68 +1535,75 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>barrnaturskog</t>
-        </is>
+          <t>lövrik, luckig gammal barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AN9" t="n">
+        <v>1</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>1 substratenheter # gammal sälg, 30 cm i diameter, lutande</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>56824820</v>
+        <v>89046255</v>
       </c>
       <c r="B10" t="n">
-        <v>78739</v>
+        <v>83298</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>492</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hötjärnberget, Ång</t>
+          <t>Hötjärnsbergets nordsida, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>684971</v>
+        <v>684817</v>
       </c>
       <c r="R10" t="n">
-        <v>7095609</v>
+        <v>7095787</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,12 +1630,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
+          <t>2020-08-31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
+          <t>2020-08-31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1622,33 +1649,40 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>barrnaturskog</t>
-        </is>
+          <t>lövrik, halvfuktig grannaturskog i nordlut</t>
+        </is>
+      </c>
+      <c r="AN10" t="n">
+        <v>1</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>1 substratenheter # murken ved i stamärr vid basen av gammal björk</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>56824800</v>
+        <v>87754483</v>
       </c>
       <c r="B11" t="n">
-        <v>78980</v>
+        <v>83173</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1656,34 +1690,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hötjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>685567</v>
+        <v>684838</v>
       </c>
       <c r="R11" t="n">
-        <v>7095234</v>
+        <v>7095823</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,12 +1747,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
+          <t>2020-08-18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
+          <t>2020-08-18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1724,38 +1761,33 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>56824818</v>
+        <v>89046254</v>
       </c>
       <c r="B12" t="n">
-        <v>78980</v>
+        <v>92732</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1763,34 +1795,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>2014</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hötjärnberget, Ång</t>
+          <t>Hötjärnsbergets nordsida, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>684974</v>
+        <v>684816</v>
       </c>
       <c r="R12" t="n">
-        <v>7095574</v>
+        <v>7095794</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1817,12 +1849,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
+          <t>2020-08-31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
+          <t>2020-08-31</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1836,55 +1868,62 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>barrnaturskog</t>
-        </is>
+          <t>lövrik, halvfuktig grannaturskog i nordlut</t>
+        </is>
+      </c>
+      <c r="AN12" t="n">
+        <v>1</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>1 substratenheter # relativt grov asplåga, delvis barkfallen</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>89046257</v>
+        <v>89046253</v>
       </c>
       <c r="B13" t="n">
-        <v>79059</v>
+        <v>91893</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>864</v>
+        <v>4660</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1894,10 +1933,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>684808</v>
+        <v>684865</v>
       </c>
       <c r="R13" t="n">
-        <v>7095549</v>
+        <v>7095792</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1943,7 +1982,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>lövrik, luckig gammal barrnaturskog</t>
+          <t>lövrik, frisk gammal barrskog i nordlut</t>
         </is>
       </c>
       <c r="AN13" t="n">
@@ -1951,7 +1990,7 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>1 substratenheter # bark på urgammal vårtbjörk, 50 cm i diameter</t>
+          <t>1 substratenheter # runt 150-årig asp, 25 cm bred</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -1973,45 +2012,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126380525</v>
+        <v>56824851</v>
       </c>
       <c r="B14" t="n">
-        <v>98361</v>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Övre Nyland, Ång</t>
+          <t>Hötjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>684912</v>
+        <v>684861</v>
       </c>
       <c r="R14" t="n">
-        <v>7095755</v>
+        <v>7095891</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2038,12 +2077,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2054,26 +2093,36 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Carl Jansson, Rolf Nylinder</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>16846967</v>
+        <v>56824852</v>
       </c>
       <c r="B15" t="n">
-        <v>91195</v>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2081,21 +2130,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>112</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2105,10 +2154,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>685259</v>
+        <v>684845</v>
       </c>
       <c r="R15" t="n">
-        <v>7095393</v>
+        <v>7095888</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2135,12 +2184,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2013-06-01</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2013-06-01</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2154,37 +2203,33 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>barrnaturskog</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>nedbruten granlåga</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Niina Sallmén, sofia nordin</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>56824805</v>
+        <v>56824853</v>
       </c>
       <c r="B16" t="n">
-        <v>80083</v>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2216,10 +2261,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>685609</v>
+        <v>684837</v>
       </c>
       <c r="R16" t="n">
-        <v>7095258</v>
+        <v>7095870</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2288,10 +2333,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>56824793</v>
+        <v>56824854</v>
       </c>
       <c r="B17" t="n">
-        <v>80083</v>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2323,10 +2368,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>685627</v>
+        <v>684838</v>
       </c>
       <c r="R17" t="n">
-        <v>7095203</v>
+        <v>7095829</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2395,54 +2440,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>89046256</v>
+        <v>56824857</v>
       </c>
       <c r="B18" t="n">
-        <v>92197</v>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4787</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granriska</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lactarius zonarioides</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Kühner &amp; Romagn.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hötjärnsbergets nordsida, Ång</t>
+          <t>Hötjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>684780</v>
+        <v>684806</v>
       </c>
       <c r="R18" t="n">
-        <v>7095590</v>
+        <v>7095721</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2469,12 +2505,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2488,67 +2524,68 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>gammal örtrik grannaturskog med gamla lövträd</t>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>89046255</v>
+        <v>56824858</v>
       </c>
       <c r="B19" t="n">
-        <v>75066</v>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>492</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hötjärnsbergets nordsida, Ång</t>
+          <t>Hötjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>684817</v>
+        <v>684801</v>
       </c>
       <c r="R19" t="n">
-        <v>7095787</v>
+        <v>7095676</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2575,12 +2612,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2594,75 +2631,68 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>lövrik, halvfuktig grannaturskog i nordlut</t>
-        </is>
-      </c>
-      <c r="AN19" t="n">
-        <v>1</v>
+          <t>barrnaturskog</t>
+        </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>1 substratenheter # murken ved i stamärr vid basen av gammal björk</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>89046259</v>
+        <v>56824859</v>
       </c>
       <c r="B20" t="n">
-        <v>80043</v>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hötjärnsbergets nordsida, Ång</t>
+          <t>Hötjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>684835</v>
+        <v>684806</v>
       </c>
       <c r="R20" t="n">
-        <v>7095545</v>
+        <v>7095684</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2689,12 +2719,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2708,62 +2738,55 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>lövrik, luckig gammal barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AN20" t="n">
-        <v>1</v>
+          <t>barrnaturskog</t>
+        </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>1 substratenheter # gammal sälg, 30 cm i diameter, lutande</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>56824840</v>
+        <v>56824860</v>
       </c>
       <c r="B21" t="n">
-        <v>80119</v>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2773,10 +2796,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>685646</v>
+        <v>684802</v>
       </c>
       <c r="R21" t="n">
-        <v>7095420</v>
+        <v>7095650</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2845,10 +2868,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>56824836</v>
+        <v>56824862</v>
       </c>
       <c r="B22" t="n">
-        <v>80083</v>
+        <v>80432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2880,10 +2903,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>685530</v>
+        <v>684797</v>
       </c>
       <c r="R22" t="n">
-        <v>7095541</v>
+        <v>7095623</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2952,10 +2975,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>56824835</v>
+        <v>56824863</v>
       </c>
       <c r="B23" t="n">
-        <v>78980</v>
+        <v>80432</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2963,21 +2986,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2987,10 +3010,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>685543</v>
+        <v>684829</v>
       </c>
       <c r="R23" t="n">
-        <v>7095491</v>
+        <v>7095603</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3041,7 +3064,7 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3059,32 +3082,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>56824787</v>
+        <v>56824864</v>
       </c>
       <c r="B24" t="n">
-        <v>80083</v>
+        <v>80461</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3094,10 +3117,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>685792</v>
+        <v>684829</v>
       </c>
       <c r="R24" t="n">
-        <v>7095173</v>
+        <v>7095603</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3166,45 +3189,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>89046260</v>
+        <v>56824861</v>
       </c>
       <c r="B25" t="n">
-        <v>91819</v>
+        <v>80468</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>760</v>
+        <v>6464</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Hötjärnsbergets nordsida, Ång</t>
+          <t>Hötjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>684852</v>
+        <v>684802</v>
       </c>
       <c r="R25" t="n">
-        <v>7095559</v>
+        <v>7095650</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3231,12 +3254,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3250,62 +3273,55 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>lövrik, luckig gammal barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AN25" t="n">
-        <v>1</v>
+          <t>barrnaturskog</t>
+        </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>1 substratenheter # gammal sälg, 25 cm i diameter</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>56824833</v>
+        <v>56824855</v>
       </c>
       <c r="B26" t="n">
-        <v>57657</v>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3315,10 +3331,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>685325</v>
+        <v>684831</v>
       </c>
       <c r="R26" t="n">
-        <v>7095451</v>
+        <v>7095817</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3365,11 +3381,6 @@
       <c r="AI26" t="inlineStr">
         <is>
           <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3387,10 +3398,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>56824871</v>
+        <v>126380525</v>
       </c>
       <c r="B27" t="n">
-        <v>98361</v>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3418,14 +3429,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Hötjärnberget, Ång</t>
+          <t>Övre Nyland, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>684938</v>
+        <v>684912</v>
       </c>
       <c r="R27" t="n">
-        <v>7095610</v>
+        <v>7095755</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3452,12 +3463,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3468,31 +3479,26 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Carl Jansson, Rolf Nylinder</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>56824790</v>
+        <v>16846967</v>
       </c>
       <c r="B28" t="n">
-        <v>80083</v>
+        <v>91859</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3500,21 +3506,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>112</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3524,10 +3530,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>685634</v>
+        <v>685259</v>
       </c>
       <c r="R28" t="n">
-        <v>7095215</v>
+        <v>7095393</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3554,12 +3560,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
+          <t>2013-06-01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
+          <t>2013-06-01</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3573,33 +3579,37 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>barrnaturskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>nedbruten granlåga</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Niina Sallmén</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
+          <t>Niina Sallmén, sofia nordin</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>56824786</v>
+        <v>56824828</v>
       </c>
       <c r="B29" t="n">
-        <v>91263</v>
+        <v>81312</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3607,21 +3617,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>1049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3631,10 +3641,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>685877</v>
+        <v>685204</v>
       </c>
       <c r="R29" t="n">
-        <v>7095154</v>
+        <v>7095464</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3685,7 +3695,7 @@
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>torrgran/granlåga</t>
+          <t>högstubbe tall</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3706,7 +3716,7 @@
         <v>56824831</v>
       </c>
       <c r="B30" t="n">
-        <v>80955</v>
+        <v>81312</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3810,45 +3820,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>56824874</v>
+        <v>87754468</v>
       </c>
       <c r="B31" t="n">
-        <v>78980</v>
+        <v>91920</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Hötjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>685011</v>
+        <v>685442</v>
       </c>
       <c r="R31" t="n">
-        <v>7095785</v>
+        <v>7095261</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3875,12 +3888,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
+          <t>2020-08-18</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
+          <t>2020-08-18</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3889,73 +3902,64 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>gammeltall</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>56824813</v>
+        <v>126716319</v>
       </c>
       <c r="B32" t="n">
-        <v>80083</v>
+        <v>91920</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Hötjärnberget, Ång</t>
+          <t>Björkmyran, Björkmyran, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>685343</v>
+        <v>685442</v>
       </c>
       <c r="R32" t="n">
-        <v>7095317</v>
+        <v>7095256</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3982,12 +3986,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3998,58 +4002,48 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Herman Niva</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Herman Niva</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>56824834</v>
+        <v>56824825</v>
       </c>
       <c r="B33" t="n">
-        <v>92535</v>
+        <v>83173</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4059,10 +4053,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>685531</v>
+        <v>685171</v>
       </c>
       <c r="R33" t="n">
-        <v>7095430</v>
+        <v>7095583</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4109,6 +4103,11 @@
       <c r="AI33" t="inlineStr">
         <is>
           <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>gammal gran</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4126,32 +4125,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>56824812</v>
+        <v>56824822</v>
       </c>
       <c r="B34" t="n">
-        <v>98361</v>
+        <v>93197</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4161,10 +4160,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>685354</v>
+        <v>685000</v>
       </c>
       <c r="R34" t="n">
-        <v>7095296</v>
+        <v>7095521</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4228,45 +4227,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126715777</v>
+        <v>56824810</v>
       </c>
       <c r="B35" t="n">
-        <v>80083</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Hötjärnberget, Hötjärnberget, Ång</t>
+          <t>Hötjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>685267</v>
+        <v>685462</v>
       </c>
       <c r="R35" t="n">
-        <v>7095385</v>
+        <v>7095229</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4293,12 +4292,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4309,30 +4308,40 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Herman Niva</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Herman Niva</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>56824837</v>
+        <v>56824818</v>
       </c>
       <c r="B36" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -4360,10 +4369,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>685526</v>
+        <v>684974</v>
       </c>
       <c r="R36" t="n">
-        <v>7095623</v>
+        <v>7095574</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4414,7 +4423,7 @@
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>gammeltall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4432,32 +4441,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>56824788</v>
+        <v>56824826</v>
       </c>
       <c r="B37" t="n">
-        <v>80083</v>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4467,10 +4476,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>685755</v>
+        <v>685176</v>
       </c>
       <c r="R37" t="n">
-        <v>7095204</v>
+        <v>7095463</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4521,7 +4530,7 @@
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4539,32 +4548,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>56824860</v>
+        <v>56824829</v>
       </c>
       <c r="B38" t="n">
-        <v>80083</v>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4574,10 +4583,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>684802</v>
+        <v>685219</v>
       </c>
       <c r="R38" t="n">
-        <v>7095650</v>
+        <v>7095463</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4628,7 +4637,7 @@
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gammeltall</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4646,10 +4655,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>56824858</v>
+        <v>56824813</v>
       </c>
       <c r="B39" t="n">
-        <v>80083</v>
+        <v>80432</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4681,10 +4690,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>684801</v>
+        <v>685343</v>
       </c>
       <c r="R39" t="n">
-        <v>7095676</v>
+        <v>7095317</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4753,10 +4762,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>56824876</v>
+        <v>56824815</v>
       </c>
       <c r="B40" t="n">
-        <v>80083</v>
+        <v>80432</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4788,10 +4797,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>685010</v>
+        <v>685221</v>
       </c>
       <c r="R40" t="n">
-        <v>7095847</v>
+        <v>7095364</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4860,55 +4869,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>56202571</v>
+        <v>56824823</v>
       </c>
       <c r="B41" t="n">
-        <v>56633</v>
+        <v>80432</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100045</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Hötjärnberget, Övre Nyland, Ång</t>
+          <t>Hötjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>684943</v>
+        <v>685044</v>
       </c>
       <c r="R41" t="n">
-        <v>7095874</v>
+        <v>7095491</v>
       </c>
       <c r="S41" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4932,12 +4934,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2015-07-15</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2015-07-15</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4948,26 +4950,36 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ulf Hallin</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ulf Hallin</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>56824825</v>
+        <v>56824824</v>
       </c>
       <c r="B42" t="n">
-        <v>82792</v>
+        <v>80432</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4975,21 +4987,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4999,10 +5011,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>685171</v>
+        <v>685178</v>
       </c>
       <c r="R42" t="n">
-        <v>7095583</v>
+        <v>7095579</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5053,7 +5065,7 @@
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>gammal gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5071,32 +5083,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>56824795</v>
+        <v>56824830</v>
       </c>
       <c r="B43" t="n">
-        <v>80118</v>
+        <v>80432</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5106,10 +5118,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>685627</v>
+        <v>685248</v>
       </c>
       <c r="R43" t="n">
-        <v>7095192</v>
+        <v>7095440</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5178,32 +5190,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>56824808</v>
+        <v>56824867</v>
       </c>
       <c r="B44" t="n">
-        <v>98361</v>
+        <v>80432</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5213,10 +5225,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>685444</v>
+        <v>684918</v>
       </c>
       <c r="R44" t="n">
-        <v>7095311</v>
+        <v>7095587</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5263,6 +5275,11 @@
       <c r="AI44" t="inlineStr">
         <is>
           <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>asp</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5280,45 +5297,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>56824791</v>
+        <v>126715218</v>
       </c>
       <c r="B45" t="n">
-        <v>80119</v>
+        <v>80432</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Hötjärnberget, Ång</t>
+          <t>Hötjärnberget, Hötjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>685634</v>
+        <v>685175</v>
       </c>
       <c r="R45" t="n">
-        <v>7095215</v>
+        <v>7095429</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5345,12 +5362,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5361,71 +5378,61 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Herman Niva</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Herman Niva</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>56824822</v>
+        <v>126715777</v>
       </c>
       <c r="B46" t="n">
-        <v>92535</v>
+        <v>80432</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Hötjärnberget, Ång</t>
+          <t>Hötjärnberget, Hötjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>685000</v>
+        <v>685267</v>
       </c>
       <c r="R46" t="n">
-        <v>7095521</v>
+        <v>7095385</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5452,12 +5459,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5468,53 +5475,48 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Herman Niva</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Herman Niva</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>56824829</v>
+        <v>56824868</v>
       </c>
       <c r="B47" t="n">
-        <v>78980</v>
+        <v>80461</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5524,10 +5526,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>685219</v>
+        <v>684918</v>
       </c>
       <c r="R47" t="n">
-        <v>7095463</v>
+        <v>7095587</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5578,7 +5580,7 @@
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>gammeltall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5596,32 +5598,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>56824823</v>
+        <v>56824869</v>
       </c>
       <c r="B48" t="n">
-        <v>80083</v>
+        <v>80468</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5631,10 +5633,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>685044</v>
+        <v>684918</v>
       </c>
       <c r="R48" t="n">
-        <v>7095491</v>
+        <v>7095587</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5685,7 +5687,7 @@
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5703,10 +5705,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>56824794</v>
+        <v>56824833</v>
       </c>
       <c r="B49" t="n">
-        <v>80083</v>
+        <v>57953</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5714,21 +5716,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5738,10 +5740,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>685627</v>
+        <v>685325</v>
       </c>
       <c r="R49" t="n">
-        <v>7095192</v>
+        <v>7095451</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5792,7 +5794,7 @@
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -5810,32 +5812,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>56824873</v>
+        <v>56824817</v>
       </c>
       <c r="B50" t="n">
-        <v>98361</v>
+        <v>5495</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>101410</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5845,10 +5847,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>684964</v>
+        <v>685095</v>
       </c>
       <c r="R50" t="n">
-        <v>7095723</v>
+        <v>7095401</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5895,6 +5897,11 @@
       <c r="AI50" t="inlineStr">
         <is>
           <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>gammal tall</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -5912,32 +5919,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>56824814</v>
+        <v>56824808</v>
       </c>
       <c r="B51" t="n">
-        <v>98382</v>
+        <v>99118</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5947,10 +5954,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>685343</v>
+        <v>685444</v>
       </c>
       <c r="R51" t="n">
-        <v>7095317</v>
+        <v>7095311</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5997,11 +6004,6 @@
       <c r="AI51" t="inlineStr">
         <is>
           <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>sälg</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6019,32 +6021,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>56824854</v>
+        <v>56824811</v>
       </c>
       <c r="B52" t="n">
-        <v>80083</v>
+        <v>99118</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6054,10 +6056,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>684838</v>
+        <v>685373</v>
       </c>
       <c r="R52" t="n">
-        <v>7095829</v>
+        <v>7095204</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6104,11 +6106,6 @@
       <c r="AI52" t="inlineStr">
         <is>
           <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>sälg</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6126,32 +6123,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>56824866</v>
+        <v>56824812</v>
       </c>
       <c r="B53" t="n">
-        <v>91256</v>
+        <v>99118</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1205</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6161,10 +6158,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>684881</v>
+        <v>685354</v>
       </c>
       <c r="R53" t="n">
-        <v>7095539</v>
+        <v>7095296</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6211,11 +6208,6 @@
       <c r="AI53" t="inlineStr">
         <is>
           <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>asp</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6233,32 +6225,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>56824862</v>
+        <v>56824814</v>
       </c>
       <c r="B54" t="n">
-        <v>80083</v>
+        <v>99140</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6268,10 +6260,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>684797</v>
+        <v>685343</v>
       </c>
       <c r="R54" t="n">
-        <v>7095623</v>
+        <v>7095317</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6340,10 +6332,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>56824797</v>
+        <v>56824816</v>
       </c>
       <c r="B55" t="n">
-        <v>80083</v>
+        <v>79085</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6351,21 +6343,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6375,10 +6367,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>685577</v>
+        <v>685106</v>
       </c>
       <c r="R55" t="n">
-        <v>7095199</v>
+        <v>7095395</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6429,7 +6421,7 @@
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6447,10 +6439,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>56824809</v>
+        <v>56824821</v>
       </c>
       <c r="B56" t="n">
-        <v>91263</v>
+        <v>79085</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6458,21 +6450,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5432</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6482,10 +6474,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>685441</v>
+        <v>685006</v>
       </c>
       <c r="R56" t="n">
-        <v>7095291</v>
+        <v>7095576</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6536,7 +6528,7 @@
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>torrgran/granlåga</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -6554,32 +6546,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>56824804</v>
+        <v>56824827</v>
       </c>
       <c r="B57" t="n">
-        <v>80112</v>
+        <v>79085</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6589,10 +6581,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>685577</v>
+        <v>685176</v>
       </c>
       <c r="R57" t="n">
-        <v>7095238</v>
+        <v>7095463</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6643,7 +6635,7 @@
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>brandstubbe omgärdade av 3 gammeltallar</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -6661,45 +6653,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126380523</v>
+        <v>56824870</v>
       </c>
       <c r="B58" t="n">
-        <v>78980</v>
+        <v>80392</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Övre Nyland, Ång</t>
+          <t>Hötjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>684940</v>
+        <v>684918</v>
       </c>
       <c r="R58" t="n">
-        <v>7095766</v>
+        <v>7095587</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6726,12 +6718,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6743,62 +6735,57 @@
       <c r="AG58" t="b">
         <v>0</v>
       </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Carl Jansson, Rolf Nylinder</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>56824859</v>
+        <v>56824875</v>
       </c>
       <c r="B59" t="n">
-        <v>80083</v>
+        <v>97231</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>2869</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6808,10 +6795,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>684806</v>
+        <v>685024</v>
       </c>
       <c r="R59" t="n">
-        <v>7095684</v>
+        <v>7095843</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6858,11 +6845,6 @@
       <c r="AI59" t="inlineStr">
         <is>
           <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>sälg</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -6880,32 +6862,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>56824864</v>
+        <v>56824872</v>
       </c>
       <c r="B60" t="n">
-        <v>80112</v>
+        <v>79327</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6915,10 +6897,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>684829</v>
+        <v>684965</v>
       </c>
       <c r="R60" t="n">
-        <v>7095603</v>
+        <v>7095699</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6969,7 +6951,7 @@
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -6987,32 +6969,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>56824819</v>
+        <v>56824874</v>
       </c>
       <c r="B61" t="n">
-        <v>78738</v>
+        <v>79327</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7022,10 +7004,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>684971</v>
+        <v>685011</v>
       </c>
       <c r="R61" t="n">
-        <v>7095609</v>
+        <v>7095785</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7076,7 +7058,7 @@
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>gammeltall</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7094,45 +7076,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>89046253</v>
+        <v>126380523</v>
       </c>
       <c r="B62" t="n">
-        <v>91229</v>
+        <v>79327</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4660</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Hötjärnsbergets nordsida, Ång</t>
+          <t>Övre Nyland, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>684865</v>
+        <v>684940</v>
       </c>
       <c r="R62" t="n">
-        <v>7095792</v>
+        <v>7095766</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7159,12 +7141,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7176,42 +7158,40 @@
       <c r="AG62" t="b">
         <v>0</v>
       </c>
-      <c r="AI62" t="inlineStr">
-        <is>
-          <t>lövrik, frisk gammal barrskog i nordlut</t>
-        </is>
-      </c>
-      <c r="AN62" t="n">
-        <v>1</v>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>1 substratenheter # runt 150-årig asp, 25 cm bred</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Carl Jansson, Rolf Nylinder</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>56824867</v>
+        <v>56824819</v>
       </c>
       <c r="B63" t="n">
-        <v>80083</v>
+        <v>79084</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7219,21 +7199,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7243,10 +7223,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>684918</v>
+        <v>684971</v>
       </c>
       <c r="R63" t="n">
-        <v>7095587</v>
+        <v>7095609</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7297,7 +7277,7 @@
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7315,32 +7295,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>56824855</v>
+        <v>56824876</v>
       </c>
       <c r="B64" t="n">
-        <v>98361</v>
+        <v>80432</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7350,10 +7330,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>684831</v>
+        <v>685010</v>
       </c>
       <c r="R64" t="n">
-        <v>7095817</v>
+        <v>7095847</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7400,6 +7380,11 @@
       <c r="AI64" t="inlineStr">
         <is>
           <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -7417,10 +7402,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>56824830</v>
+        <v>126380524</v>
       </c>
       <c r="B65" t="n">
-        <v>80083</v>
+        <v>80432</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7448,14 +7433,14 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Hötjärnberget, Ång</t>
+          <t>Övre Nyland, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>685248</v>
+        <v>684940</v>
       </c>
       <c r="R65" t="n">
-        <v>7095440</v>
+        <v>7095767</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7482,12 +7467,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7499,35 +7484,40 @@
       <c r="AG65" t="b">
         <v>0</v>
       </c>
-      <c r="AI65" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Carl Jansson, Rolf Nylinder</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>56824875</v>
+        <v>54419611</v>
       </c>
       <c r="B66" t="n">
-        <v>96487</v>
+        <v>56925</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7535,37 +7525,44 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2869</v>
+        <v>100045</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Hötjärnberget, Ång</t>
+          <t>Lapptjärn, Övre Nyland, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>685024</v>
+        <v>684981</v>
       </c>
       <c r="R66" t="n">
-        <v>7095843</v>
+        <v>7095879</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7589,12 +7586,27 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
+          <t>2015-07-15</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
+          <t>2015-07-15</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>2 vuxna och 3 ungar</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7605,69 +7617,71 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AI66" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Ulf Hallin</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Ulf Hallin</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126715218</v>
+        <v>56202571</v>
       </c>
       <c r="B67" t="n">
-        <v>80083</v>
+        <v>56925</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>100045</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Hötjärnberget, Hötjärnberget, Ång</t>
+          <t>Hötjärnberget, Övre Nyland, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>685175</v>
+        <v>684943</v>
       </c>
       <c r="R67" t="n">
-        <v>7095429</v>
+        <v>7095874</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7691,12 +7705,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2015-07-15</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2015-07-15</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7711,44 +7725,44 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Herman Niva</t>
+          <t>Ulf Hallin</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Herman Niva</t>
+          <t>Ulf Hallin</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>56824851</v>
+        <v>56824871</v>
       </c>
       <c r="B68" t="n">
-        <v>80083</v>
+        <v>99118</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7758,10 +7772,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>684861</v>
+        <v>684938</v>
       </c>
       <c r="R68" t="n">
-        <v>7095891</v>
+        <v>7095610</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7808,11 +7822,6 @@
       <c r="AI68" t="inlineStr">
         <is>
           <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>sälg</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -7830,32 +7839,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>56824852</v>
+        <v>56824873</v>
       </c>
       <c r="B69" t="n">
-        <v>80083</v>
+        <v>99118</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7865,10 +7874,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>684845</v>
+        <v>684964</v>
       </c>
       <c r="R69" t="n">
-        <v>7095888</v>
+        <v>7095723</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7915,11 +7924,6 @@
       <c r="AI69" t="inlineStr">
         <is>
           <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>sälg</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -7937,10 +7941,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>56824801</v>
+        <v>56824820</v>
       </c>
       <c r="B70" t="n">
-        <v>80083</v>
+        <v>79085</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7948,21 +7952,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7972,10 +7976,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>685577</v>
+        <v>684971</v>
       </c>
       <c r="R70" t="n">
-        <v>7095238</v>
+        <v>7095609</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8026,7 +8030,7 @@
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8044,10 +8048,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>56824806</v>
+        <v>56824784</v>
       </c>
       <c r="B71" t="n">
-        <v>82792</v>
+        <v>83173</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8079,10 +8083,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>685621</v>
+        <v>685882</v>
       </c>
       <c r="R71" t="n">
-        <v>7095321</v>
+        <v>7095130</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8151,10 +8155,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>56824838</v>
+        <v>56824806</v>
       </c>
       <c r="B72" t="n">
-        <v>77929</v>
+        <v>83173</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8162,21 +8166,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6487</v>
+        <v>1312</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8186,10 +8190,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>685580</v>
+        <v>685621</v>
       </c>
       <c r="R72" t="n">
-        <v>7095719</v>
+        <v>7095321</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8240,7 +8244,7 @@
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>törvedsstubbe</t>
+          <t>gammal gran</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -8258,45 +8262,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>89046254</v>
+        <v>56824783</v>
       </c>
       <c r="B73" t="n">
-        <v>92045</v>
+        <v>96338</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2014</v>
+        <v>2809</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Hötjärnsbergets nordsida, Ång</t>
+          <t>Hötjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>684816</v>
+        <v>685894</v>
       </c>
       <c r="R73" t="n">
-        <v>7095794</v>
+        <v>7095123</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8323,12 +8327,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8342,78 +8346,63 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>lövrik, halvfuktig grannaturskog i nordlut</t>
-        </is>
-      </c>
-      <c r="AN73" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>1 substratenheter # relativt grov asplåga, delvis barkfallen</t>
+          <t>barrnaturskog</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY73" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>87754500</v>
+        <v>56824834</v>
       </c>
       <c r="B74" t="n">
-        <v>91256</v>
+        <v>93197</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1205</v>
+        <v>4364</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Hötjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>684863</v>
+        <v>685531</v>
       </c>
       <c r="R74" t="n">
-        <v>7095572</v>
+        <v>7095430</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8440,12 +8429,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2020-08-18</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2020-08-18</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8454,33 +8443,33 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>87754468</v>
+        <v>56824782</v>
       </c>
       <c r="B75" t="n">
-        <v>91256</v>
+        <v>91872</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8488,37 +8477,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1205</v>
+        <v>5447</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Hötjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>685442</v>
+        <v>685887</v>
       </c>
       <c r="R75" t="n">
-        <v>7095261</v>
+        <v>7095094</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8545,12 +8531,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2020-08-18</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2020-08-18</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8559,51 +8545,60 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>56824821</v>
+        <v>56824800</v>
       </c>
       <c r="B76" t="n">
-        <v>78739</v>
+        <v>79327</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8613,10 +8608,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>685006</v>
+        <v>685567</v>
       </c>
       <c r="R76" t="n">
-        <v>7095576</v>
+        <v>7095234</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8667,7 +8662,7 @@
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -8685,32 +8680,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>56824868</v>
+        <v>56824835</v>
       </c>
       <c r="B77" t="n">
-        <v>80112</v>
+        <v>79327</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8720,10 +8715,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>684918</v>
+        <v>685543</v>
       </c>
       <c r="R77" t="n">
-        <v>7095587</v>
+        <v>7095491</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8774,7 +8769,7 @@
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -8792,32 +8787,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>56824789</v>
+        <v>56824787</v>
       </c>
       <c r="B78" t="n">
-        <v>80119</v>
+        <v>80432</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8827,10 +8822,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>685755</v>
+        <v>685792</v>
       </c>
       <c r="R78" t="n">
-        <v>7095204</v>
+        <v>7095173</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8899,32 +8894,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>56824811</v>
+        <v>56824788</v>
       </c>
       <c r="B79" t="n">
-        <v>98361</v>
+        <v>80432</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8934,7 +8929,7 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>685373</v>
+        <v>685755</v>
       </c>
       <c r="R79" t="n">
         <v>7095204</v>
@@ -8984,6 +8979,11 @@
       <c r="AI79" t="inlineStr">
         <is>
           <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -9001,10 +9001,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>56824817</v>
+        <v>56824790</v>
       </c>
       <c r="B80" t="n">
-        <v>5492</v>
+        <v>80432</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9012,21 +9012,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>101410</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9036,10 +9036,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>685095</v>
+        <v>685634</v>
       </c>
       <c r="R80" t="n">
-        <v>7095401</v>
+        <v>7095215</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9090,7 +9090,7 @@
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>gammal tall</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -9108,10 +9108,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>56824865</v>
+        <v>56824793</v>
       </c>
       <c r="B81" t="n">
-        <v>80083</v>
+        <v>80432</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9143,10 +9143,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>684847</v>
+        <v>685627</v>
       </c>
       <c r="R81" t="n">
-        <v>7095566</v>
+        <v>7095203</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9197,7 +9197,7 @@
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -9215,32 +9215,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>56824861</v>
+        <v>56824794</v>
       </c>
       <c r="B82" t="n">
-        <v>80119</v>
+        <v>80432</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9250,10 +9250,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>684802</v>
+        <v>685627</v>
       </c>
       <c r="R82" t="n">
-        <v>7095650</v>
+        <v>7095192</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9322,10 +9322,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>56824810</v>
+        <v>56824797</v>
       </c>
       <c r="B83" t="n">
-        <v>78980</v>
+        <v>80432</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9333,21 +9333,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9357,10 +9357,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>685462</v>
+        <v>685577</v>
       </c>
       <c r="R83" t="n">
-        <v>7095229</v>
+        <v>7095199</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9411,7 +9411,7 @@
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -9429,10 +9429,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>56824826</v>
+        <v>56824798</v>
       </c>
       <c r="B84" t="n">
-        <v>78980</v>
+        <v>80432</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9440,21 +9440,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9464,10 +9464,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>685176</v>
+        <v>685574</v>
       </c>
       <c r="R84" t="n">
-        <v>7095463</v>
+        <v>7095206</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9518,7 +9518,7 @@
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -9536,10 +9536,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>87754483</v>
+        <v>56824801</v>
       </c>
       <c r="B85" t="n">
-        <v>82792</v>
+        <v>80432</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9547,37 +9547,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Hötjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>684838</v>
+        <v>685577</v>
       </c>
       <c r="R85" t="n">
-        <v>7095823</v>
+        <v>7095238</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9604,12 +9601,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2020-08-18</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2020-08-18</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9618,33 +9615,38 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
+      </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AY85" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>56824785</v>
+        <v>56824805</v>
       </c>
       <c r="B86" t="n">
-        <v>91263</v>
+        <v>80432</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9652,21 +9654,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9676,10 +9678,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>685889</v>
+        <v>685609</v>
       </c>
       <c r="R86" t="n">
-        <v>7095140</v>
+        <v>7095258</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9730,7 +9732,7 @@
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>torrgran/granlåga</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -9748,10 +9750,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>56824853</v>
+        <v>56824836</v>
       </c>
       <c r="B87" t="n">
-        <v>80083</v>
+        <v>80432</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9783,10 +9785,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>684837</v>
+        <v>685530</v>
       </c>
       <c r="R87" t="n">
-        <v>7095870</v>
+        <v>7095541</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9855,32 +9857,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>56824863</v>
+        <v>56824796</v>
       </c>
       <c r="B88" t="n">
-        <v>80083</v>
+        <v>80461</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9890,10 +9892,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>684829</v>
+        <v>685627</v>
       </c>
       <c r="R88" t="n">
-        <v>7095603</v>
+        <v>7095192</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9962,10 +9964,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>56824783</v>
+        <v>56824804</v>
       </c>
       <c r="B89" t="n">
-        <v>95594</v>
+        <v>80461</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9973,21 +9975,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2809</v>
+        <v>6462</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9997,10 +9999,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>685894</v>
+        <v>685577</v>
       </c>
       <c r="R89" t="n">
-        <v>7095123</v>
+        <v>7095238</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10047,6 +10049,11 @@
       <c r="AI89" t="inlineStr">
         <is>
           <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -10064,60 +10071,48 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120279029</v>
+        <v>56824792</v>
       </c>
       <c r="B90" t="n">
-        <v>98361</v>
+        <v>80467</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Skog, Ång</t>
+          <t>Hötjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>685668</v>
+        <v>685634</v>
       </c>
       <c r="R90" t="n">
-        <v>7095162</v>
+        <v>7095215</v>
       </c>
       <c r="S90" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10141,12 +10136,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10155,29 +10150,38 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
+      </c>
+      <c r="AI90" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Albin Larsson Ekström</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Albin Larsson Ekström</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>56824792</v>
+        <v>56824795</v>
       </c>
       <c r="B91" t="n">
-        <v>80118</v>
+        <v>80467</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10209,10 +10213,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>685634</v>
+        <v>685627</v>
       </c>
       <c r="R91" t="n">
-        <v>7095215</v>
+        <v>7095192</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10281,32 +10285,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>56824815</v>
+        <v>56824803</v>
       </c>
       <c r="B92" t="n">
-        <v>80083</v>
+        <v>80467</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10316,10 +10320,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>685221</v>
+        <v>685577</v>
       </c>
       <c r="R92" t="n">
-        <v>7095364</v>
+        <v>7095238</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10388,10 +10392,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126716319</v>
+        <v>56824789</v>
       </c>
       <c r="B93" t="n">
-        <v>91256</v>
+        <v>80468</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10399,34 +10403,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1205</v>
+        <v>6464</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Björkmyran, Björkmyran, Ång</t>
+          <t>Hötjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>685442</v>
+        <v>685755</v>
       </c>
       <c r="R93" t="n">
-        <v>7095256</v>
+        <v>7095204</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10453,12 +10457,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10469,61 +10473,71 @@
       </c>
       <c r="AG93" t="b">
         <v>0</v>
+      </c>
+      <c r="AI93" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Herman Niva</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Herman Niva</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>16846900</v>
+        <v>56824791</v>
       </c>
       <c r="B94" t="n">
-        <v>82792</v>
+        <v>80468</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1312</v>
+        <v>6464</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Blåbergssjön, Ång</t>
+          <t>Hötjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>685798</v>
+        <v>685634</v>
       </c>
       <c r="R94" t="n">
-        <v>7095734</v>
+        <v>7095215</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10550,12 +10564,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2013-05-31</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2013-05-31</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10569,59 +10583,55 @@
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>Bäckgranskog</t>
+          <t>barrnaturskog</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>gammal gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Niina Sallmén, sofia nordin</t>
-        </is>
-      </c>
-      <c r="AY94" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>56824784</v>
+        <v>56824840</v>
       </c>
       <c r="B95" t="n">
-        <v>82792</v>
+        <v>80468</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1312</v>
+        <v>6464</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10631,10 +10641,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>685882</v>
+        <v>685646</v>
       </c>
       <c r="R95" t="n">
-        <v>7095130</v>
+        <v>7095420</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10685,7 +10695,7 @@
       </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>gammal gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -10703,55 +10713,60 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>54419611</v>
+        <v>120279029</v>
       </c>
       <c r="B96" t="n">
-        <v>56633</v>
+        <v>99118</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100045</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Lapptjärn, Övre Nyland, Ång</t>
+          <t>Skog, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>684981</v>
+        <v>685668</v>
       </c>
       <c r="R96" t="n">
-        <v>7095879</v>
+        <v>7095162</v>
       </c>
       <c r="S96" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10775,27 +10790,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2015-07-15</t>
-        </is>
-      </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2015-07-15</t>
-        </is>
-      </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>2 vuxna och 3 ungar</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10804,28 +10804,29 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Ulf Hallin</t>
+          <t>Albin Larsson Ekström</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Ulf Hallin</t>
+          <t>Albin Larsson Ekström</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>56824816</v>
+        <v>16846900</v>
       </c>
       <c r="B97" t="n">
-        <v>78739</v>
+        <v>83173</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10833,34 +10834,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>228912</v>
+        <v>1312</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Hötjärnberget, Ång</t>
+          <t>Blåbergssjön, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>685106</v>
+        <v>685798</v>
       </c>
       <c r="R97" t="n">
-        <v>7095395</v>
+        <v>7095734</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10887,12 +10888,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
+          <t>2013-05-31</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
+          <t>2013-05-31</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10906,55 +10907,59 @@
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>barrnaturskog</t>
+          <t>Bäckgranskog</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>gammal gran</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Niina Sallmén</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY97" t="inlineStr"/>
+          <t>sofia nordin, Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>56824856</v>
+        <v>56824837</v>
       </c>
       <c r="B98" t="n">
-        <v>91263</v>
+        <v>79327</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10964,10 +10969,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>684829</v>
+        <v>685526</v>
       </c>
       <c r="R98" t="n">
-        <v>7095792</v>
+        <v>7095623</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11018,7 +11023,7 @@
       </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>torrgran/granlåga</t>
+          <t>gammeltall</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -11036,10 +11041,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>56824872</v>
+        <v>56824838</v>
       </c>
       <c r="B99" t="n">
-        <v>78980</v>
+        <v>78334</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11047,21 +11052,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11071,10 +11076,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>684965</v>
+        <v>685580</v>
       </c>
       <c r="R99" t="n">
-        <v>7095699</v>
+        <v>7095719</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11125,7 +11130,7 @@
       </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>törvedsstubbe</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>
@@ -11143,32 +11148,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>56824803</v>
+        <v>56824839</v>
       </c>
       <c r="B100" t="n">
-        <v>80118</v>
+        <v>79350</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6463</v>
+        <v>260591</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11178,10 +11183,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>685577</v>
+        <v>685595</v>
       </c>
       <c r="R100" t="n">
-        <v>7095238</v>
+        <v>7095735</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11232,7 +11237,7 @@
       </c>
       <c r="AO100" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -11247,225 +11252,6 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" t="n">
-        <v>56824796</v>
-      </c>
-      <c r="B101" t="n">
-        <v>80112</v>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E101" t="n">
-        <v>6462</v>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>Stuplav</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
-      <c r="P101" t="inlineStr">
-        <is>
-          <t>Hötjärnberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q101" t="n">
-        <v>685627</v>
-      </c>
-      <c r="R101" t="n">
-        <v>7095192</v>
-      </c>
-      <c r="S101" t="n">
-        <v>10</v>
-      </c>
-      <c r="T101" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U101" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="V101" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W101" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="Y101" t="inlineStr">
-        <is>
-          <t>2015-05-18</t>
-        </is>
-      </c>
-      <c r="AA101" t="inlineStr">
-        <is>
-          <t>2015-10-30</t>
-        </is>
-      </c>
-      <c r="AD101" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE101" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG101" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI101" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO101" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AT101" t="inlineStr"/>
-      <c r="AW101" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AX101" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY101" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" t="n">
-        <v>126380524</v>
-      </c>
-      <c r="B102" t="n">
-        <v>80083</v>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E102" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
-      <c r="P102" t="inlineStr">
-        <is>
-          <t>Övre Nyland, Ång</t>
-        </is>
-      </c>
-      <c r="Q102" t="n">
-        <v>684940</v>
-      </c>
-      <c r="R102" t="n">
-        <v>7095767</v>
-      </c>
-      <c r="S102" t="n">
-        <v>10</v>
-      </c>
-      <c r="T102" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U102" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="V102" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W102" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="Y102" t="inlineStr">
-        <is>
-          <t>2025-06-24</t>
-        </is>
-      </c>
-      <c r="AA102" t="inlineStr">
-        <is>
-          <t>2025-06-24</t>
-        </is>
-      </c>
-      <c r="AD102" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE102" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG102" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ102" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK102" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO102" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AT102" t="inlineStr"/>
-      <c r="AW102" t="inlineStr">
-        <is>
-          <t>Carl Jansson</t>
-        </is>
-      </c>
-      <c r="AX102" t="inlineStr">
-        <is>
-          <t>Carl Jansson, Rolf Nylinder</t>
-        </is>
-      </c>
-      <c r="AY102" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
